--- a/Template_Keuangan.xlsx
+++ b/Template_Keuangan.xlsx
@@ -8,9 +8,7 @@
     <sheet name="Grafik" sheetId="4" r:id="rId4"/>
     <sheet name="Pengaturan" sheetId="5" r:id="rId5"/>
     <sheet name="Pagu Harian" sheetId="6" r:id="rId6"/>
-    <sheet name="Pengeluaran Pangan" sheetId="7" r:id="rId7"/>
-    <sheet name="Pengeluaran Operasional" sheetId="8" r:id="rId8"/>
-    <sheet name="Kategori" sheetId="9" r:id="rId9"/>
+    <sheet name="Kategori" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -332,7 +330,7 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -355,6 +353,52 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF70AD47"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF2E75B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -541,9 +585,6 @@
       </a:solidFill>
     </a:ln>
   </c:spPr>
-  <c:externalData r:id="rId1">
-    <c:autoUpdate val="0"/>
-  </c:externalData>
 </c:chartSpace>
 </file>
 
@@ -1470,7 +1511,7 @@
         <f>Pengaturan!B10</f>
       </c>
       <c r="B6" s="24">
-        <f>'Pengeluaran Pangan'!G125+'Pengeluaran Operasional'!G123</f>
+        <f>SUM('Rekap Harian'!$F$6:$F$36)+SUM('Rekap Harian'!$I$6:$I$36)</f>
       </c>
       <c r="C6" s="23">
         <f>A6-B6</f>
@@ -1495,7 +1536,7 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>IFERROR('Pengeluaran Pangan'!G125/Pengaturan!B5,0)</f>
+        <f>IFERROR(B14/Pengaturan!B5,0)</f>
       </c>
     </row>
     <row r="10">
@@ -1542,7 +1583,7 @@
         </is>
       </c>
       <c r="B14" s="9">
-        <f>'Pengeluaran Pangan'!G125</f>
+        <f>SUM('Rekap Harian'!$F$6:$F$36)</f>
       </c>
     </row>
     <row r="15">
@@ -1581,7 +1622,7 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>IFERROR('Pengeluaran Operasional'!G123/Pengaturan!B5,0)</f>
+        <f>IFERROR(B24/Pengaturan!B5,0)</f>
       </c>
     </row>
     <row r="20">
@@ -1628,7 +1669,7 @@
         </is>
       </c>
       <c r="B24" s="9">
-        <f>'Pengeluaran Operasional'!G123</f>
+        <f>SUM('Rekap Harian'!$I$6:$I$36)</f>
       </c>
     </row>
     <row r="25">
@@ -1759,7 +1800,7 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jumlah Hari DEFISIT (boros)</t>
+          <t xml:space="preserve">Jumlah Hari DEFISIT (melewati pagu)</t>
         </is>
       </c>
       <c r="B40" s="15">
@@ -1777,93 +1818,103 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jumlah Hari Belum Input</t>
+        </is>
+      </c>
+      <c r="B42" s="15">
+        <f>COUNTIF('Rekap Harian'!N6:N36,"BELUM")</f>
+      </c>
+    </row>
+    <row r="43">
 </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Total Akumulasi Surplus</t>
-        </is>
-      </c>
-      <c r="B43" s="10">
-        <f>SUMIF('Rekap Harian'!M6:M36,"&gt;0")</f>
-      </c>
-    </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total Akumulasi Defisit</t>
-        </is>
-      </c>
-      <c r="B44" s="9">
-        <f>SUMIF('Rekap Harian'!M6:M36,"&lt;0")</f>
+          <t xml:space="preserve">Total Akumulasi Surplus</t>
+        </is>
+      </c>
+      <c r="B44" s="10">
+        <f>SUMIF('Rekap Harian'!M6:M36,"&gt;0")</f>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Total Akumulasi Defisit</t>
+        </is>
+      </c>
+      <c r="B45" s="9">
+        <f>SUMIF('Rekap Harian'!M6:M36,"&lt;0")</f>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Net Surplus/Defisit</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>B43+B44</f>
-      </c>
-    </row>
-    <row r="46">
+      <c r="B46" s="7">
+        <f>B44+B45</f>
+      </c>
+    </row>
+    <row r="47">
 </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pengeluaran Tertinggi/Hari</t>
-        </is>
-      </c>
-      <c r="B47" s="9">
-        <f>MAX('Rekap Harian'!L6:L36)</f>
-      </c>
-    </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pengeluaran Tertinggi/Hari</t>
+        </is>
+      </c>
+      <c r="B48" s="9">
+        <f>MAX('Rekap Harian'!L6:L36)</f>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Pengeluaran Terendah/Hari</t>
         </is>
       </c>
-      <c r="B48" s="10">
-        <f>MINIFS('Rekap Harian'!L6:L36,'Rekap Harian'!L6:L36,"&gt;0")</f>
-      </c>
-    </row>
-    <row r="49">
+      <c r="B49" s="10">
+        <f>IFERROR(MINIFS('Rekap Harian'!L6:L36,'Rekap Harian'!L6:L36,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="50">
 </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">CATATAN:</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Dashboard update otomatis dari sheet lain. Edit hanya di Pengaturan, Pagu Harian, &amp; Log Pengeluaran.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Selisih/Surplus POSITIF = hemat, NEGATIF = boros.</t>
+          <t xml:space="preserve">- Dashboard update otomatis dari sheet Rekap Harian.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Lihat detail harian di 'Rekap Harian', detail mingguan di 'Rekap Mingguan'.</t>
+          <t xml:space="preserve">- Input aktual di sheet 'Rekap Harian' kolom F (Pangan) &amp; kolom I (Operasional).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Visualisasi tersedia di sheet 'Grafik'.</t>
+          <t xml:space="preserve">- Selisih/Surplus POSITIF = hemat, NEGATIF = boros (melewati pagu).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Lihat detail mingguan di 'Rekap Mingguan', visualisasi di 'Grafik'.</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1958,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Setiap hari akan dihitung otomatis: pagu, aktual, selisih, dan status surplus/defisit</t>
+          <t xml:space="preserve">Input aktual pangan (kolom F) &amp; operasional (kolom I) setiap hari. Sisanya otomatis.</t>
         </is>
       </c>
     </row>
@@ -2012,31 +2063,31 @@
         <f>IFERROR(VLOOKUP(B6,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
       <c r="F6" s="3">
-        <f>IF(B6="",0,SUMIF('Pengeluaran Pangan'!A:A,B6,'Pengeluaran Pangan'!G:G))</f>
+        <v>1790000</v>
       </c>
       <c r="G6" s="17">
-        <f>IF(B6="",0,E6-F6)</f>
+        <f>IF(B6="",0,E6-IF(F6="",0,F6))</f>
       </c>
       <c r="H6" s="3">
         <f>IFERROR(VLOOKUP(B6,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
       <c r="I6" s="3">
-        <f>IF(B6="",0,SUMIF('Pengeluaran Operasional'!A:A,B6,'Pengeluaran Operasional'!G:G))</f>
+        <v>555000</v>
       </c>
       <c r="J6" s="17">
-        <f>IF(B6="",0,H6-I6)</f>
+        <f>IF(B6="",0,H6-IF(I6="",0,I6))</f>
       </c>
       <c r="K6" s="14">
         <f>E6+H6</f>
       </c>
       <c r="L6" s="14">
-        <f>F6+I6</f>
+        <f>IF(F6="",0,F6)+IF(I6="",0,I6)</f>
       </c>
       <c r="M6" s="17">
         <f>K6-L6</f>
       </c>
-      <c r="N6" s="26">
-        <f>IF(B6="","",IF(M6&gt;0,"SURPLUS",IF(M6&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N6" s="29">
+        <f>IF(B6="","",IF(AND(F6="",I6=""),"BELUM",IF(M6&gt;0,"SURPLUS",IF(M6&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="7">
@@ -2056,31 +2107,31 @@
         <f>IFERROR(VLOOKUP(B7,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
       <c r="F7" s="3">
-        <f>IF(B7="",0,SUMIF('Pengeluaran Pangan'!A:A,B7,'Pengeluaran Pangan'!G:G))</f>
+        <v>1650000</v>
       </c>
       <c r="G7" s="17">
-        <f>IF(B7="",0,E7-F7)</f>
+        <f>IF(B7="",0,E7-IF(F7="",0,F7))</f>
       </c>
       <c r="H7" s="3">
         <f>IFERROR(VLOOKUP(B7,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
       <c r="I7" s="3">
-        <f>IF(B7="",0,SUMIF('Pengeluaran Operasional'!A:A,B7,'Pengeluaran Operasional'!G:G))</f>
+        <v>600000</v>
       </c>
       <c r="J7" s="17">
-        <f>IF(B7="",0,H7-I7)</f>
+        <f>IF(B7="",0,H7-IF(I7="",0,I7))</f>
       </c>
       <c r="K7" s="14">
         <f>E7+H7</f>
       </c>
       <c r="L7" s="14">
-        <f>F7+I7</f>
+        <f>IF(F7="",0,F7)+IF(I7="",0,I7)</f>
       </c>
       <c r="M7" s="17">
         <f>K7-L7</f>
       </c>
-      <c r="N7" s="26">
-        <f>IF(B7="","",IF(M7&gt;0,"SURPLUS",IF(M7&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N7" s="29">
+        <f>IF(B7="","",IF(AND(F7="",I7=""),"BELUM",IF(M7&gt;0,"SURPLUS",IF(M7&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="8">
@@ -2100,31 +2151,31 @@
         <f>IFERROR(VLOOKUP(B8,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
       <c r="F8" s="3">
-        <f>IF(B8="",0,SUMIF('Pengeluaran Pangan'!A:A,B8,'Pengeluaran Pangan'!G:G))</f>
+        <v>1980000</v>
       </c>
       <c r="G8" s="17">
-        <f>IF(B8="",0,E8-F8)</f>
+        <f>IF(B8="",0,E8-IF(F8="",0,F8))</f>
       </c>
       <c r="H8" s="3">
         <f>IFERROR(VLOOKUP(B8,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
       <c r="I8" s="3">
-        <f>IF(B8="",0,SUMIF('Pengeluaran Operasional'!A:A,B8,'Pengeluaran Operasional'!G:G))</f>
+        <v>700000</v>
       </c>
       <c r="J8" s="17">
-        <f>IF(B8="",0,H8-I8)</f>
+        <f>IF(B8="",0,H8-IF(I8="",0,I8))</f>
       </c>
       <c r="K8" s="14">
         <f>E8+H8</f>
       </c>
       <c r="L8" s="14">
-        <f>F8+I8</f>
+        <f>IF(F8="",0,F8)+IF(I8="",0,I8)</f>
       </c>
       <c r="M8" s="17">
         <f>K8-L8</f>
       </c>
-      <c r="N8" s="26">
-        <f>IF(B8="","",IF(M8&gt;0,"SURPLUS",IF(M8&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N8" s="29">
+        <f>IF(B8="","",IF(AND(F8="",I8=""),"BELUM",IF(M8&gt;0,"SURPLUS",IF(M8&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="9">
@@ -2144,31 +2195,31 @@
         <f>IFERROR(VLOOKUP(B9,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
       <c r="F9" s="3">
-        <f>IF(B9="",0,SUMIF('Pengeluaran Pangan'!A:A,B9,'Pengeluaran Pangan'!G:G))</f>
+        <v>1450000</v>
       </c>
       <c r="G9" s="17">
-        <f>IF(B9="",0,E9-F9)</f>
+        <f>IF(B9="",0,E9-IF(F9="",0,F9))</f>
       </c>
       <c r="H9" s="3">
         <f>IFERROR(VLOOKUP(B9,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
       <c r="I9" s="3">
-        <f>IF(B9="",0,SUMIF('Pengeluaran Operasional'!A:A,B9,'Pengeluaran Operasional'!G:G))</f>
+        <v>480000</v>
       </c>
       <c r="J9" s="17">
-        <f>IF(B9="",0,H9-I9)</f>
+        <f>IF(B9="",0,H9-IF(I9="",0,I9))</f>
       </c>
       <c r="K9" s="14">
         <f>E9+H9</f>
       </c>
       <c r="L9" s="14">
-        <f>F9+I9</f>
+        <f>IF(F9="",0,F9)+IF(I9="",0,I9)</f>
       </c>
       <c r="M9" s="17">
         <f>K9-L9</f>
       </c>
-      <c r="N9" s="26">
-        <f>IF(B9="","",IF(M9&gt;0,"SURPLUS",IF(M9&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N9" s="29">
+        <f>IF(B9="","",IF(AND(F9="",I9=""),"BELUM",IF(M9&gt;0,"SURPLUS",IF(M9&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="10">
@@ -2188,31 +2239,31 @@
         <f>IFERROR(VLOOKUP(B10,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
       <c r="F10" s="3">
-        <f>IF(B10="",0,SUMIF('Pengeluaran Pangan'!A:A,B10,'Pengeluaran Pangan'!G:G))</f>
+        <v>2100000</v>
       </c>
       <c r="G10" s="17">
-        <f>IF(B10="",0,E10-F10)</f>
+        <f>IF(B10="",0,E10-IF(F10="",0,F10))</f>
       </c>
       <c r="H10" s="3">
         <f>IFERROR(VLOOKUP(B10,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
       <c r="I10" s="3">
-        <f>IF(B10="",0,SUMIF('Pengeluaran Operasional'!A:A,B10,'Pengeluaran Operasional'!G:G))</f>
+        <v>850000</v>
       </c>
       <c r="J10" s="17">
-        <f>IF(B10="",0,H10-I10)</f>
+        <f>IF(B10="",0,H10-IF(I10="",0,I10))</f>
       </c>
       <c r="K10" s="14">
         <f>E10+H10</f>
       </c>
       <c r="L10" s="14">
-        <f>F10+I10</f>
+        <f>IF(F10="",0,F10)+IF(I10="",0,I10)</f>
       </c>
       <c r="M10" s="17">
         <f>K10-L10</f>
       </c>
-      <c r="N10" s="26">
-        <f>IF(B10="","",IF(M10&gt;0,"SURPLUS",IF(M10&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N10" s="29">
+        <f>IF(B10="","",IF(AND(F10="",I10=""),"BELUM",IF(M10&gt;0,"SURPLUS",IF(M10&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="11">
@@ -2231,32 +2282,26 @@
       <c r="E11" s="3">
         <f>IFERROR(VLOOKUP(B11,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F11" s="3">
-        <f>IF(B11="",0,SUMIF('Pengeluaran Pangan'!A:A,B11,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G11" s="17">
-        <f>IF(B11="",0,E11-F11)</f>
+        <f>IF(B11="",0,E11-IF(F11="",0,F11))</f>
       </c>
       <c r="H11" s="3">
         <f>IFERROR(VLOOKUP(B11,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I11" s="3">
-        <f>IF(B11="",0,SUMIF('Pengeluaran Operasional'!A:A,B11,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J11" s="17">
-        <f>IF(B11="",0,H11-I11)</f>
+        <f>IF(B11="",0,H11-IF(I11="",0,I11))</f>
       </c>
       <c r="K11" s="14">
         <f>E11+H11</f>
       </c>
       <c r="L11" s="14">
-        <f>F11+I11</f>
+        <f>IF(F11="",0,F11)+IF(I11="",0,I11)</f>
       </c>
       <c r="M11" s="17">
         <f>K11-L11</f>
       </c>
-      <c r="N11" s="26">
-        <f>IF(B11="","",IF(M11&gt;0,"SURPLUS",IF(M11&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N11" s="29">
+        <f>IF(B11="","",IF(AND(F11="",I11=""),"BELUM",IF(M11&gt;0,"SURPLUS",IF(M11&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="12">
@@ -2275,32 +2320,26 @@
       <c r="E12" s="3">
         <f>IFERROR(VLOOKUP(B12,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F12" s="3">
-        <f>IF(B12="",0,SUMIF('Pengeluaran Pangan'!A:A,B12,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G12" s="17">
-        <f>IF(B12="",0,E12-F12)</f>
+        <f>IF(B12="",0,E12-IF(F12="",0,F12))</f>
       </c>
       <c r="H12" s="3">
         <f>IFERROR(VLOOKUP(B12,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I12" s="3">
-        <f>IF(B12="",0,SUMIF('Pengeluaran Operasional'!A:A,B12,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J12" s="17">
-        <f>IF(B12="",0,H12-I12)</f>
+        <f>IF(B12="",0,H12-IF(I12="",0,I12))</f>
       </c>
       <c r="K12" s="14">
         <f>E12+H12</f>
       </c>
       <c r="L12" s="14">
-        <f>F12+I12</f>
+        <f>IF(F12="",0,F12)+IF(I12="",0,I12)</f>
       </c>
       <c r="M12" s="17">
         <f>K12-L12</f>
       </c>
-      <c r="N12" s="26">
-        <f>IF(B12="","",IF(M12&gt;0,"SURPLUS",IF(M12&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N12" s="29">
+        <f>IF(B12="","",IF(AND(F12="",I12=""),"BELUM",IF(M12&gt;0,"SURPLUS",IF(M12&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="13">
@@ -2319,32 +2358,26 @@
       <c r="E13" s="3">
         <f>IFERROR(VLOOKUP(B13,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F13" s="3">
-        <f>IF(B13="",0,SUMIF('Pengeluaran Pangan'!A:A,B13,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G13" s="17">
-        <f>IF(B13="",0,E13-F13)</f>
+        <f>IF(B13="",0,E13-IF(F13="",0,F13))</f>
       </c>
       <c r="H13" s="3">
         <f>IFERROR(VLOOKUP(B13,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I13" s="3">
-        <f>IF(B13="",0,SUMIF('Pengeluaran Operasional'!A:A,B13,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J13" s="17">
-        <f>IF(B13="",0,H13-I13)</f>
+        <f>IF(B13="",0,H13-IF(I13="",0,I13))</f>
       </c>
       <c r="K13" s="14">
         <f>E13+H13</f>
       </c>
       <c r="L13" s="14">
-        <f>F13+I13</f>
+        <f>IF(F13="",0,F13)+IF(I13="",0,I13)</f>
       </c>
       <c r="M13" s="17">
         <f>K13-L13</f>
       </c>
-      <c r="N13" s="26">
-        <f>IF(B13="","",IF(M13&gt;0,"SURPLUS",IF(M13&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N13" s="29">
+        <f>IF(B13="","",IF(AND(F13="",I13=""),"BELUM",IF(M13&gt;0,"SURPLUS",IF(M13&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="14">
@@ -2363,32 +2396,26 @@
       <c r="E14" s="3">
         <f>IFERROR(VLOOKUP(B14,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F14" s="3">
-        <f>IF(B14="",0,SUMIF('Pengeluaran Pangan'!A:A,B14,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G14" s="17">
-        <f>IF(B14="",0,E14-F14)</f>
+        <f>IF(B14="",0,E14-IF(F14="",0,F14))</f>
       </c>
       <c r="H14" s="3">
         <f>IFERROR(VLOOKUP(B14,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I14" s="3">
-        <f>IF(B14="",0,SUMIF('Pengeluaran Operasional'!A:A,B14,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J14" s="17">
-        <f>IF(B14="",0,H14-I14)</f>
+        <f>IF(B14="",0,H14-IF(I14="",0,I14))</f>
       </c>
       <c r="K14" s="14">
         <f>E14+H14</f>
       </c>
       <c r="L14" s="14">
-        <f>F14+I14</f>
+        <f>IF(F14="",0,F14)+IF(I14="",0,I14)</f>
       </c>
       <c r="M14" s="17">
         <f>K14-L14</f>
       </c>
-      <c r="N14" s="26">
-        <f>IF(B14="","",IF(M14&gt;0,"SURPLUS",IF(M14&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N14" s="29">
+        <f>IF(B14="","",IF(AND(F14="",I14=""),"BELUM",IF(M14&gt;0,"SURPLUS",IF(M14&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="15">
@@ -2407,32 +2434,26 @@
       <c r="E15" s="3">
         <f>IFERROR(VLOOKUP(B15,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F15" s="3">
-        <f>IF(B15="",0,SUMIF('Pengeluaran Pangan'!A:A,B15,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G15" s="17">
-        <f>IF(B15="",0,E15-F15)</f>
+        <f>IF(B15="",0,E15-IF(F15="",0,F15))</f>
       </c>
       <c r="H15" s="3">
         <f>IFERROR(VLOOKUP(B15,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I15" s="3">
-        <f>IF(B15="",0,SUMIF('Pengeluaran Operasional'!A:A,B15,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J15" s="17">
-        <f>IF(B15="",0,H15-I15)</f>
+        <f>IF(B15="",0,H15-IF(I15="",0,I15))</f>
       </c>
       <c r="K15" s="14">
         <f>E15+H15</f>
       </c>
       <c r="L15" s="14">
-        <f>F15+I15</f>
+        <f>IF(F15="",0,F15)+IF(I15="",0,I15)</f>
       </c>
       <c r="M15" s="17">
         <f>K15-L15</f>
       </c>
-      <c r="N15" s="26">
-        <f>IF(B15="","",IF(M15&gt;0,"SURPLUS",IF(M15&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N15" s="29">
+        <f>IF(B15="","",IF(AND(F15="",I15=""),"BELUM",IF(M15&gt;0,"SURPLUS",IF(M15&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="16">
@@ -2451,32 +2472,26 @@
       <c r="E16" s="3">
         <f>IFERROR(VLOOKUP(B16,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F16" s="3">
-        <f>IF(B16="",0,SUMIF('Pengeluaran Pangan'!A:A,B16,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G16" s="17">
-        <f>IF(B16="",0,E16-F16)</f>
+        <f>IF(B16="",0,E16-IF(F16="",0,F16))</f>
       </c>
       <c r="H16" s="3">
         <f>IFERROR(VLOOKUP(B16,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I16" s="3">
-        <f>IF(B16="",0,SUMIF('Pengeluaran Operasional'!A:A,B16,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J16" s="17">
-        <f>IF(B16="",0,H16-I16)</f>
+        <f>IF(B16="",0,H16-IF(I16="",0,I16))</f>
       </c>
       <c r="K16" s="14">
         <f>E16+H16</f>
       </c>
       <c r="L16" s="14">
-        <f>F16+I16</f>
+        <f>IF(F16="",0,F16)+IF(I16="",0,I16)</f>
       </c>
       <c r="M16" s="17">
         <f>K16-L16</f>
       </c>
-      <c r="N16" s="26">
-        <f>IF(B16="","",IF(M16&gt;0,"SURPLUS",IF(M16&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N16" s="29">
+        <f>IF(B16="","",IF(AND(F16="",I16=""),"BELUM",IF(M16&gt;0,"SURPLUS",IF(M16&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="17">
@@ -2495,32 +2510,26 @@
       <c r="E17" s="3">
         <f>IFERROR(VLOOKUP(B17,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F17" s="3">
-        <f>IF(B17="",0,SUMIF('Pengeluaran Pangan'!A:A,B17,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G17" s="17">
-        <f>IF(B17="",0,E17-F17)</f>
+        <f>IF(B17="",0,E17-IF(F17="",0,F17))</f>
       </c>
       <c r="H17" s="3">
         <f>IFERROR(VLOOKUP(B17,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I17" s="3">
-        <f>IF(B17="",0,SUMIF('Pengeluaran Operasional'!A:A,B17,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J17" s="17">
-        <f>IF(B17="",0,H17-I17)</f>
+        <f>IF(B17="",0,H17-IF(I17="",0,I17))</f>
       </c>
       <c r="K17" s="14">
         <f>E17+H17</f>
       </c>
       <c r="L17" s="14">
-        <f>F17+I17</f>
+        <f>IF(F17="",0,F17)+IF(I17="",0,I17)</f>
       </c>
       <c r="M17" s="17">
         <f>K17-L17</f>
       </c>
-      <c r="N17" s="26">
-        <f>IF(B17="","",IF(M17&gt;0,"SURPLUS",IF(M17&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N17" s="29">
+        <f>IF(B17="","",IF(AND(F17="",I17=""),"BELUM",IF(M17&gt;0,"SURPLUS",IF(M17&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="18">
@@ -2539,32 +2548,26 @@
       <c r="E18" s="3">
         <f>IFERROR(VLOOKUP(B18,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F18" s="3">
-        <f>IF(B18="",0,SUMIF('Pengeluaran Pangan'!A:A,B18,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G18" s="17">
-        <f>IF(B18="",0,E18-F18)</f>
+        <f>IF(B18="",0,E18-IF(F18="",0,F18))</f>
       </c>
       <c r="H18" s="3">
         <f>IFERROR(VLOOKUP(B18,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I18" s="3">
-        <f>IF(B18="",0,SUMIF('Pengeluaran Operasional'!A:A,B18,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J18" s="17">
-        <f>IF(B18="",0,H18-I18)</f>
+        <f>IF(B18="",0,H18-IF(I18="",0,I18))</f>
       </c>
       <c r="K18" s="14">
         <f>E18+H18</f>
       </c>
       <c r="L18" s="14">
-        <f>F18+I18</f>
+        <f>IF(F18="",0,F18)+IF(I18="",0,I18)</f>
       </c>
       <c r="M18" s="17">
         <f>K18-L18</f>
       </c>
-      <c r="N18" s="26">
-        <f>IF(B18="","",IF(M18&gt;0,"SURPLUS",IF(M18&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N18" s="29">
+        <f>IF(B18="","",IF(AND(F18="",I18=""),"BELUM",IF(M18&gt;0,"SURPLUS",IF(M18&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="19">
@@ -2583,32 +2586,26 @@
       <c r="E19" s="3">
         <f>IFERROR(VLOOKUP(B19,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F19" s="3">
-        <f>IF(B19="",0,SUMIF('Pengeluaran Pangan'!A:A,B19,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G19" s="17">
-        <f>IF(B19="",0,E19-F19)</f>
+        <f>IF(B19="",0,E19-IF(F19="",0,F19))</f>
       </c>
       <c r="H19" s="3">
         <f>IFERROR(VLOOKUP(B19,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I19" s="3">
-        <f>IF(B19="",0,SUMIF('Pengeluaran Operasional'!A:A,B19,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J19" s="17">
-        <f>IF(B19="",0,H19-I19)</f>
+        <f>IF(B19="",0,H19-IF(I19="",0,I19))</f>
       </c>
       <c r="K19" s="14">
         <f>E19+H19</f>
       </c>
       <c r="L19" s="14">
-        <f>F19+I19</f>
+        <f>IF(F19="",0,F19)+IF(I19="",0,I19)</f>
       </c>
       <c r="M19" s="17">
         <f>K19-L19</f>
       </c>
-      <c r="N19" s="26">
-        <f>IF(B19="","",IF(M19&gt;0,"SURPLUS",IF(M19&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N19" s="29">
+        <f>IF(B19="","",IF(AND(F19="",I19=""),"BELUM",IF(M19&gt;0,"SURPLUS",IF(M19&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="20">
@@ -2627,32 +2624,26 @@
       <c r="E20" s="3">
         <f>IFERROR(VLOOKUP(B20,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F20" s="3">
-        <f>IF(B20="",0,SUMIF('Pengeluaran Pangan'!A:A,B20,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G20" s="17">
-        <f>IF(B20="",0,E20-F20)</f>
+        <f>IF(B20="",0,E20-IF(F20="",0,F20))</f>
       </c>
       <c r="H20" s="3">
         <f>IFERROR(VLOOKUP(B20,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I20" s="3">
-        <f>IF(B20="",0,SUMIF('Pengeluaran Operasional'!A:A,B20,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J20" s="17">
-        <f>IF(B20="",0,H20-I20)</f>
+        <f>IF(B20="",0,H20-IF(I20="",0,I20))</f>
       </c>
       <c r="K20" s="14">
         <f>E20+H20</f>
       </c>
       <c r="L20" s="14">
-        <f>F20+I20</f>
+        <f>IF(F20="",0,F20)+IF(I20="",0,I20)</f>
       </c>
       <c r="M20" s="17">
         <f>K20-L20</f>
       </c>
-      <c r="N20" s="26">
-        <f>IF(B20="","",IF(M20&gt;0,"SURPLUS",IF(M20&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N20" s="29">
+        <f>IF(B20="","",IF(AND(F20="",I20=""),"BELUM",IF(M20&gt;0,"SURPLUS",IF(M20&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="21">
@@ -2671,32 +2662,26 @@
       <c r="E21" s="3">
         <f>IFERROR(VLOOKUP(B21,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F21" s="3">
-        <f>IF(B21="",0,SUMIF('Pengeluaran Pangan'!A:A,B21,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G21" s="17">
-        <f>IF(B21="",0,E21-F21)</f>
+        <f>IF(B21="",0,E21-IF(F21="",0,F21))</f>
       </c>
       <c r="H21" s="3">
         <f>IFERROR(VLOOKUP(B21,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I21" s="3">
-        <f>IF(B21="",0,SUMIF('Pengeluaran Operasional'!A:A,B21,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J21" s="17">
-        <f>IF(B21="",0,H21-I21)</f>
+        <f>IF(B21="",0,H21-IF(I21="",0,I21))</f>
       </c>
       <c r="K21" s="14">
         <f>E21+H21</f>
       </c>
       <c r="L21" s="14">
-        <f>F21+I21</f>
+        <f>IF(F21="",0,F21)+IF(I21="",0,I21)</f>
       </c>
       <c r="M21" s="17">
         <f>K21-L21</f>
       </c>
-      <c r="N21" s="26">
-        <f>IF(B21="","",IF(M21&gt;0,"SURPLUS",IF(M21&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N21" s="29">
+        <f>IF(B21="","",IF(AND(F21="",I21=""),"BELUM",IF(M21&gt;0,"SURPLUS",IF(M21&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="22">
@@ -2715,32 +2700,26 @@
       <c r="E22" s="3">
         <f>IFERROR(VLOOKUP(B22,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F22" s="3">
-        <f>IF(B22="",0,SUMIF('Pengeluaran Pangan'!A:A,B22,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G22" s="17">
-        <f>IF(B22="",0,E22-F22)</f>
+        <f>IF(B22="",0,E22-IF(F22="",0,F22))</f>
       </c>
       <c r="H22" s="3">
         <f>IFERROR(VLOOKUP(B22,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I22" s="3">
-        <f>IF(B22="",0,SUMIF('Pengeluaran Operasional'!A:A,B22,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J22" s="17">
-        <f>IF(B22="",0,H22-I22)</f>
+        <f>IF(B22="",0,H22-IF(I22="",0,I22))</f>
       </c>
       <c r="K22" s="14">
         <f>E22+H22</f>
       </c>
       <c r="L22" s="14">
-        <f>F22+I22</f>
+        <f>IF(F22="",0,F22)+IF(I22="",0,I22)</f>
       </c>
       <c r="M22" s="17">
         <f>K22-L22</f>
       </c>
-      <c r="N22" s="26">
-        <f>IF(B22="","",IF(M22&gt;0,"SURPLUS",IF(M22&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N22" s="29">
+        <f>IF(B22="","",IF(AND(F22="",I22=""),"BELUM",IF(M22&gt;0,"SURPLUS",IF(M22&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="23">
@@ -2759,32 +2738,26 @@
       <c r="E23" s="3">
         <f>IFERROR(VLOOKUP(B23,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F23" s="3">
-        <f>IF(B23="",0,SUMIF('Pengeluaran Pangan'!A:A,B23,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G23" s="17">
-        <f>IF(B23="",0,E23-F23)</f>
+        <f>IF(B23="",0,E23-IF(F23="",0,F23))</f>
       </c>
       <c r="H23" s="3">
         <f>IFERROR(VLOOKUP(B23,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I23" s="3">
-        <f>IF(B23="",0,SUMIF('Pengeluaran Operasional'!A:A,B23,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J23" s="17">
-        <f>IF(B23="",0,H23-I23)</f>
+        <f>IF(B23="",0,H23-IF(I23="",0,I23))</f>
       </c>
       <c r="K23" s="14">
         <f>E23+H23</f>
       </c>
       <c r="L23" s="14">
-        <f>F23+I23</f>
+        <f>IF(F23="",0,F23)+IF(I23="",0,I23)</f>
       </c>
       <c r="M23" s="17">
         <f>K23-L23</f>
       </c>
-      <c r="N23" s="26">
-        <f>IF(B23="","",IF(M23&gt;0,"SURPLUS",IF(M23&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N23" s="29">
+        <f>IF(B23="","",IF(AND(F23="",I23=""),"BELUM",IF(M23&gt;0,"SURPLUS",IF(M23&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="24">
@@ -2803,32 +2776,26 @@
       <c r="E24" s="3">
         <f>IFERROR(VLOOKUP(B24,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F24" s="3">
-        <f>IF(B24="",0,SUMIF('Pengeluaran Pangan'!A:A,B24,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G24" s="17">
-        <f>IF(B24="",0,E24-F24)</f>
+        <f>IF(B24="",0,E24-IF(F24="",0,F24))</f>
       </c>
       <c r="H24" s="3">
         <f>IFERROR(VLOOKUP(B24,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I24" s="3">
-        <f>IF(B24="",0,SUMIF('Pengeluaran Operasional'!A:A,B24,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J24" s="17">
-        <f>IF(B24="",0,H24-I24)</f>
+        <f>IF(B24="",0,H24-IF(I24="",0,I24))</f>
       </c>
       <c r="K24" s="14">
         <f>E24+H24</f>
       </c>
       <c r="L24" s="14">
-        <f>F24+I24</f>
+        <f>IF(F24="",0,F24)+IF(I24="",0,I24)</f>
       </c>
       <c r="M24" s="17">
         <f>K24-L24</f>
       </c>
-      <c r="N24" s="26">
-        <f>IF(B24="","",IF(M24&gt;0,"SURPLUS",IF(M24&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N24" s="29">
+        <f>IF(B24="","",IF(AND(F24="",I24=""),"BELUM",IF(M24&gt;0,"SURPLUS",IF(M24&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="25">
@@ -2847,32 +2814,26 @@
       <c r="E25" s="3">
         <f>IFERROR(VLOOKUP(B25,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F25" s="3">
-        <f>IF(B25="",0,SUMIF('Pengeluaran Pangan'!A:A,B25,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G25" s="17">
-        <f>IF(B25="",0,E25-F25)</f>
+        <f>IF(B25="",0,E25-IF(F25="",0,F25))</f>
       </c>
       <c r="H25" s="3">
         <f>IFERROR(VLOOKUP(B25,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I25" s="3">
-        <f>IF(B25="",0,SUMIF('Pengeluaran Operasional'!A:A,B25,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J25" s="17">
-        <f>IF(B25="",0,H25-I25)</f>
+        <f>IF(B25="",0,H25-IF(I25="",0,I25))</f>
       </c>
       <c r="K25" s="14">
         <f>E25+H25</f>
       </c>
       <c r="L25" s="14">
-        <f>F25+I25</f>
+        <f>IF(F25="",0,F25)+IF(I25="",0,I25)</f>
       </c>
       <c r="M25" s="17">
         <f>K25-L25</f>
       </c>
-      <c r="N25" s="26">
-        <f>IF(B25="","",IF(M25&gt;0,"SURPLUS",IF(M25&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N25" s="29">
+        <f>IF(B25="","",IF(AND(F25="",I25=""),"BELUM",IF(M25&gt;0,"SURPLUS",IF(M25&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="26">
@@ -2891,32 +2852,26 @@
       <c r="E26" s="3">
         <f>IFERROR(VLOOKUP(B26,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F26" s="3">
-        <f>IF(B26="",0,SUMIF('Pengeluaran Pangan'!A:A,B26,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G26" s="17">
-        <f>IF(B26="",0,E26-F26)</f>
+        <f>IF(B26="",0,E26-IF(F26="",0,F26))</f>
       </c>
       <c r="H26" s="3">
         <f>IFERROR(VLOOKUP(B26,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I26" s="3">
-        <f>IF(B26="",0,SUMIF('Pengeluaran Operasional'!A:A,B26,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J26" s="17">
-        <f>IF(B26="",0,H26-I26)</f>
+        <f>IF(B26="",0,H26-IF(I26="",0,I26))</f>
       </c>
       <c r="K26" s="14">
         <f>E26+H26</f>
       </c>
       <c r="L26" s="14">
-        <f>F26+I26</f>
+        <f>IF(F26="",0,F26)+IF(I26="",0,I26)</f>
       </c>
       <c r="M26" s="17">
         <f>K26-L26</f>
       </c>
-      <c r="N26" s="26">
-        <f>IF(B26="","",IF(M26&gt;0,"SURPLUS",IF(M26&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N26" s="29">
+        <f>IF(B26="","",IF(AND(F26="",I26=""),"BELUM",IF(M26&gt;0,"SURPLUS",IF(M26&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="27">
@@ -2935,32 +2890,26 @@
       <c r="E27" s="3">
         <f>IFERROR(VLOOKUP(B27,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F27" s="3">
-        <f>IF(B27="",0,SUMIF('Pengeluaran Pangan'!A:A,B27,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G27" s="17">
-        <f>IF(B27="",0,E27-F27)</f>
+        <f>IF(B27="",0,E27-IF(F27="",0,F27))</f>
       </c>
       <c r="H27" s="3">
         <f>IFERROR(VLOOKUP(B27,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I27" s="3">
-        <f>IF(B27="",0,SUMIF('Pengeluaran Operasional'!A:A,B27,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J27" s="17">
-        <f>IF(B27="",0,H27-I27)</f>
+        <f>IF(B27="",0,H27-IF(I27="",0,I27))</f>
       </c>
       <c r="K27" s="14">
         <f>E27+H27</f>
       </c>
       <c r="L27" s="14">
-        <f>F27+I27</f>
+        <f>IF(F27="",0,F27)+IF(I27="",0,I27)</f>
       </c>
       <c r="M27" s="17">
         <f>K27-L27</f>
       </c>
-      <c r="N27" s="26">
-        <f>IF(B27="","",IF(M27&gt;0,"SURPLUS",IF(M27&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N27" s="29">
+        <f>IF(B27="","",IF(AND(F27="",I27=""),"BELUM",IF(M27&gt;0,"SURPLUS",IF(M27&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="28">
@@ -2979,32 +2928,26 @@
       <c r="E28" s="3">
         <f>IFERROR(VLOOKUP(B28,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F28" s="3">
-        <f>IF(B28="",0,SUMIF('Pengeluaran Pangan'!A:A,B28,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G28" s="17">
-        <f>IF(B28="",0,E28-F28)</f>
+        <f>IF(B28="",0,E28-IF(F28="",0,F28))</f>
       </c>
       <c r="H28" s="3">
         <f>IFERROR(VLOOKUP(B28,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I28" s="3">
-        <f>IF(B28="",0,SUMIF('Pengeluaran Operasional'!A:A,B28,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J28" s="17">
-        <f>IF(B28="",0,H28-I28)</f>
+        <f>IF(B28="",0,H28-IF(I28="",0,I28))</f>
       </c>
       <c r="K28" s="14">
         <f>E28+H28</f>
       </c>
       <c r="L28" s="14">
-        <f>F28+I28</f>
+        <f>IF(F28="",0,F28)+IF(I28="",0,I28)</f>
       </c>
       <c r="M28" s="17">
         <f>K28-L28</f>
       </c>
-      <c r="N28" s="26">
-        <f>IF(B28="","",IF(M28&gt;0,"SURPLUS",IF(M28&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N28" s="29">
+        <f>IF(B28="","",IF(AND(F28="",I28=""),"BELUM",IF(M28&gt;0,"SURPLUS",IF(M28&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="29">
@@ -3023,32 +2966,26 @@
       <c r="E29" s="3">
         <f>IFERROR(VLOOKUP(B29,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F29" s="3">
-        <f>IF(B29="",0,SUMIF('Pengeluaran Pangan'!A:A,B29,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G29" s="17">
-        <f>IF(B29="",0,E29-F29)</f>
+        <f>IF(B29="",0,E29-IF(F29="",0,F29))</f>
       </c>
       <c r="H29" s="3">
         <f>IFERROR(VLOOKUP(B29,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I29" s="3">
-        <f>IF(B29="",0,SUMIF('Pengeluaran Operasional'!A:A,B29,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J29" s="17">
-        <f>IF(B29="",0,H29-I29)</f>
+        <f>IF(B29="",0,H29-IF(I29="",0,I29))</f>
       </c>
       <c r="K29" s="14">
         <f>E29+H29</f>
       </c>
       <c r="L29" s="14">
-        <f>F29+I29</f>
+        <f>IF(F29="",0,F29)+IF(I29="",0,I29)</f>
       </c>
       <c r="M29" s="17">
         <f>K29-L29</f>
       </c>
-      <c r="N29" s="26">
-        <f>IF(B29="","",IF(M29&gt;0,"SURPLUS",IF(M29&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N29" s="29">
+        <f>IF(B29="","",IF(AND(F29="",I29=""),"BELUM",IF(M29&gt;0,"SURPLUS",IF(M29&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="30">
@@ -3067,32 +3004,26 @@
       <c r="E30" s="3">
         <f>IFERROR(VLOOKUP(B30,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F30" s="3">
-        <f>IF(B30="",0,SUMIF('Pengeluaran Pangan'!A:A,B30,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G30" s="17">
-        <f>IF(B30="",0,E30-F30)</f>
+        <f>IF(B30="",0,E30-IF(F30="",0,F30))</f>
       </c>
       <c r="H30" s="3">
         <f>IFERROR(VLOOKUP(B30,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I30" s="3">
-        <f>IF(B30="",0,SUMIF('Pengeluaran Operasional'!A:A,B30,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J30" s="17">
-        <f>IF(B30="",0,H30-I30)</f>
+        <f>IF(B30="",0,H30-IF(I30="",0,I30))</f>
       </c>
       <c r="K30" s="14">
         <f>E30+H30</f>
       </c>
       <c r="L30" s="14">
-        <f>F30+I30</f>
+        <f>IF(F30="",0,F30)+IF(I30="",0,I30)</f>
       </c>
       <c r="M30" s="17">
         <f>K30-L30</f>
       </c>
-      <c r="N30" s="26">
-        <f>IF(B30="","",IF(M30&gt;0,"SURPLUS",IF(M30&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N30" s="29">
+        <f>IF(B30="","",IF(AND(F30="",I30=""),"BELUM",IF(M30&gt;0,"SURPLUS",IF(M30&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="31">
@@ -3111,32 +3042,26 @@
       <c r="E31" s="3">
         <f>IFERROR(VLOOKUP(B31,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F31" s="3">
-        <f>IF(B31="",0,SUMIF('Pengeluaran Pangan'!A:A,B31,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G31" s="17">
-        <f>IF(B31="",0,E31-F31)</f>
+        <f>IF(B31="",0,E31-IF(F31="",0,F31))</f>
       </c>
       <c r="H31" s="3">
         <f>IFERROR(VLOOKUP(B31,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I31" s="3">
-        <f>IF(B31="",0,SUMIF('Pengeluaran Operasional'!A:A,B31,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J31" s="17">
-        <f>IF(B31="",0,H31-I31)</f>
+        <f>IF(B31="",0,H31-IF(I31="",0,I31))</f>
       </c>
       <c r="K31" s="14">
         <f>E31+H31</f>
       </c>
       <c r="L31" s="14">
-        <f>F31+I31</f>
+        <f>IF(F31="",0,F31)+IF(I31="",0,I31)</f>
       </c>
       <c r="M31" s="17">
         <f>K31-L31</f>
       </c>
-      <c r="N31" s="26">
-        <f>IF(B31="","",IF(M31&gt;0,"SURPLUS",IF(M31&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N31" s="29">
+        <f>IF(B31="","",IF(AND(F31="",I31=""),"BELUM",IF(M31&gt;0,"SURPLUS",IF(M31&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="32">
@@ -3155,32 +3080,26 @@
       <c r="E32" s="3">
         <f>IFERROR(VLOOKUP(B32,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F32" s="3">
-        <f>IF(B32="",0,SUMIF('Pengeluaran Pangan'!A:A,B32,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G32" s="17">
-        <f>IF(B32="",0,E32-F32)</f>
+        <f>IF(B32="",0,E32-IF(F32="",0,F32))</f>
       </c>
       <c r="H32" s="3">
         <f>IFERROR(VLOOKUP(B32,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I32" s="3">
-        <f>IF(B32="",0,SUMIF('Pengeluaran Operasional'!A:A,B32,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J32" s="17">
-        <f>IF(B32="",0,H32-I32)</f>
+        <f>IF(B32="",0,H32-IF(I32="",0,I32))</f>
       </c>
       <c r="K32" s="14">
         <f>E32+H32</f>
       </c>
       <c r="L32" s="14">
-        <f>F32+I32</f>
+        <f>IF(F32="",0,F32)+IF(I32="",0,I32)</f>
       </c>
       <c r="M32" s="17">
         <f>K32-L32</f>
       </c>
-      <c r="N32" s="26">
-        <f>IF(B32="","",IF(M32&gt;0,"SURPLUS",IF(M32&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N32" s="29">
+        <f>IF(B32="","",IF(AND(F32="",I32=""),"BELUM",IF(M32&gt;0,"SURPLUS",IF(M32&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="33">
@@ -3199,32 +3118,26 @@
       <c r="E33" s="3">
         <f>IFERROR(VLOOKUP(B33,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F33" s="3">
-        <f>IF(B33="",0,SUMIF('Pengeluaran Pangan'!A:A,B33,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G33" s="17">
-        <f>IF(B33="",0,E33-F33)</f>
+        <f>IF(B33="",0,E33-IF(F33="",0,F33))</f>
       </c>
       <c r="H33" s="3">
         <f>IFERROR(VLOOKUP(B33,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I33" s="3">
-        <f>IF(B33="",0,SUMIF('Pengeluaran Operasional'!A:A,B33,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J33" s="17">
-        <f>IF(B33="",0,H33-I33)</f>
+        <f>IF(B33="",0,H33-IF(I33="",0,I33))</f>
       </c>
       <c r="K33" s="14">
         <f>E33+H33</f>
       </c>
       <c r="L33" s="14">
-        <f>F33+I33</f>
+        <f>IF(F33="",0,F33)+IF(I33="",0,I33)</f>
       </c>
       <c r="M33" s="17">
         <f>K33-L33</f>
       </c>
-      <c r="N33" s="26">
-        <f>IF(B33="","",IF(M33&gt;0,"SURPLUS",IF(M33&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N33" s="29">
+        <f>IF(B33="","",IF(AND(F33="",I33=""),"BELUM",IF(M33&gt;0,"SURPLUS",IF(M33&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="34">
@@ -3243,32 +3156,26 @@
       <c r="E34" s="3">
         <f>IFERROR(VLOOKUP(B34,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F34" s="3">
-        <f>IF(B34="",0,SUMIF('Pengeluaran Pangan'!A:A,B34,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G34" s="17">
-        <f>IF(B34="",0,E34-F34)</f>
+        <f>IF(B34="",0,E34-IF(F34="",0,F34))</f>
       </c>
       <c r="H34" s="3">
         <f>IFERROR(VLOOKUP(B34,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I34" s="3">
-        <f>IF(B34="",0,SUMIF('Pengeluaran Operasional'!A:A,B34,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J34" s="17">
-        <f>IF(B34="",0,H34-I34)</f>
+        <f>IF(B34="",0,H34-IF(I34="",0,I34))</f>
       </c>
       <c r="K34" s="14">
         <f>E34+H34</f>
       </c>
       <c r="L34" s="14">
-        <f>F34+I34</f>
+        <f>IF(F34="",0,F34)+IF(I34="",0,I34)</f>
       </c>
       <c r="M34" s="17">
         <f>K34-L34</f>
       </c>
-      <c r="N34" s="26">
-        <f>IF(B34="","",IF(M34&gt;0,"SURPLUS",IF(M34&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N34" s="29">
+        <f>IF(B34="","",IF(AND(F34="",I34=""),"BELUM",IF(M34&gt;0,"SURPLUS",IF(M34&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="35">
@@ -3287,32 +3194,26 @@
       <c r="E35" s="3">
         <f>IFERROR(VLOOKUP(B35,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F35" s="3">
-        <f>IF(B35="",0,SUMIF('Pengeluaran Pangan'!A:A,B35,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G35" s="17">
-        <f>IF(B35="",0,E35-F35)</f>
+        <f>IF(B35="",0,E35-IF(F35="",0,F35))</f>
       </c>
       <c r="H35" s="3">
         <f>IFERROR(VLOOKUP(B35,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I35" s="3">
-        <f>IF(B35="",0,SUMIF('Pengeluaran Operasional'!A:A,B35,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J35" s="17">
-        <f>IF(B35="",0,H35-I35)</f>
+        <f>IF(B35="",0,H35-IF(I35="",0,I35))</f>
       </c>
       <c r="K35" s="14">
         <f>E35+H35</f>
       </c>
       <c r="L35" s="14">
-        <f>F35+I35</f>
+        <f>IF(F35="",0,F35)+IF(I35="",0,I35)</f>
       </c>
       <c r="M35" s="17">
         <f>K35-L35</f>
       </c>
-      <c r="N35" s="26">
-        <f>IF(B35="","",IF(M35&gt;0,"SURPLUS",IF(M35&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N35" s="29">
+        <f>IF(B35="","",IF(AND(F35="",I35=""),"BELUM",IF(M35&gt;0,"SURPLUS",IF(M35&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="36">
@@ -3331,32 +3232,26 @@
       <c r="E36" s="3">
         <f>IFERROR(VLOOKUP(B36,'Pagu Harian'!$A$4:$D$40,2,FALSE),Pengaturan!$B$13)</f>
       </c>
-      <c r="F36" s="3">
-        <f>IF(B36="",0,SUMIF('Pengeluaran Pangan'!A:A,B36,'Pengeluaran Pangan'!G:G))</f>
-      </c>
       <c r="G36" s="17">
-        <f>IF(B36="",0,E36-F36)</f>
+        <f>IF(B36="",0,E36-IF(F36="",0,F36))</f>
       </c>
       <c r="H36" s="3">
         <f>IFERROR(VLOOKUP(B36,'Pagu Harian'!$A$4:$D$40,3,FALSE),Pengaturan!$B$14)</f>
       </c>
-      <c r="I36" s="3">
-        <f>IF(B36="",0,SUMIF('Pengeluaran Operasional'!A:A,B36,'Pengeluaran Operasional'!G:G))</f>
-      </c>
       <c r="J36" s="17">
-        <f>IF(B36="",0,H36-I36)</f>
+        <f>IF(B36="",0,H36-IF(I36="",0,I36))</f>
       </c>
       <c r="K36" s="14">
         <f>E36+H36</f>
       </c>
       <c r="L36" s="14">
-        <f>F36+I36</f>
+        <f>IF(F36="",0,F36)+IF(I36="",0,I36)</f>
       </c>
       <c r="M36" s="17">
         <f>K36-L36</f>
       </c>
-      <c r="N36" s="26">
-        <f>IF(B36="","",IF(M36&gt;0,"SURPLUS",IF(M36&lt;0,"DEFISIT","AMAN")))</f>
+      <c r="N36" s="29">
+        <f>IF(B36="","",IF(AND(F36="",I36=""),"BELUM",IF(M36&gt;0,"SURPLUS",IF(M36&lt;0,"DEFISIT","AMAN"))))</f>
       </c>
     </row>
     <row r="37">
@@ -3405,7 +3300,7 @@
         <f>IFERROR(AVERAGEIF(B6:B36,"&lt;&gt;",E6:E36),0)</f>
       </c>
       <c r="F39" s="7">
-        <f>IFERROR(AVERAGEIF(B6:B36,"&lt;&gt;",F6:F36),0)</f>
+        <f>IFERROR(AVERAGEIF(F6:F36,"&gt;0"),0)</f>
       </c>
       <c r="G39" s="7">
         <f>IFERROR(AVERAGEIF(B6:B36,"&lt;&gt;",G6:G36),0)</f>
@@ -3414,7 +3309,7 @@
         <f>IFERROR(AVERAGEIF(B6:B36,"&lt;&gt;",H6:H36),0)</f>
       </c>
       <c r="I39" s="7">
-        <f>IFERROR(AVERAGEIF(B6:B36,"&lt;&gt;",I6:I36),0)</f>
+        <f>IFERROR(AVERAGEIF(I6:I36,"&gt;0"),0)</f>
       </c>
       <c r="J39" s="7">
         <f>IFERROR(AVERAGEIF(B6:B36,"&lt;&gt;",J6:J36),0)</f>
@@ -3423,7 +3318,7 @@
         <f>IFERROR(AVERAGEIF(B6:B36,"&lt;&gt;",K6:K36),0)</f>
       </c>
       <c r="L39" s="7">
-        <f>IFERROR(AVERAGEIF(B6:B36,"&lt;&gt;",L6:L36),0)</f>
+        <f>IFERROR(AVERAGEIF(L6:L36,"&gt;0"),0)</f>
       </c>
       <c r="M39" s="7">
         <f>IFERROR(AVERAGEIF(B6:B36,"&lt;&gt;",M6:M36),0)</f>
@@ -3433,6 +3328,20 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
+  <conditionalFormatting sqref="N6:N36">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"SURPLUS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"DEFISIT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"AMAN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"BELUM"</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 
@@ -3567,7 +3476,7 @@
       <c r="K4" s="17">
         <f>I4-J4</f>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="29">
         <f>IF(I4=0,"",IF(K4&gt;0,"SURPLUS",IF(K4&lt;0,"DEFISIT","AMAN")))</f>
       </c>
     </row>
@@ -3605,7 +3514,7 @@
       <c r="K5" s="17">
         <f>I5-J5</f>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="29">
         <f>IF(I5=0,"",IF(K5&gt;0,"SURPLUS",IF(K5&lt;0,"DEFISIT","AMAN")))</f>
       </c>
     </row>
@@ -3643,7 +3552,7 @@
       <c r="K6" s="17">
         <f>I6-J6</f>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="29">
         <f>IF(I6=0,"",IF(K6&gt;0,"SURPLUS",IF(K6&lt;0,"DEFISIT","AMAN")))</f>
       </c>
     </row>
@@ -3681,7 +3590,7 @@
       <c r="K7" s="17">
         <f>I7-J7</f>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="29">
         <f>IF(I7=0,"",IF(K7&gt;0,"SURPLUS",IF(K7&lt;0,"DEFISIT","AMAN")))</f>
       </c>
     </row>
@@ -3719,7 +3628,7 @@
       <c r="K8" s="17">
         <f>I8-J8</f>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="29">
         <f>IF(I8=0,"",IF(K8&gt;0,"SURPLUS",IF(K8&lt;0,"DEFISIT","AMAN")))</f>
       </c>
     </row>
@@ -3763,6 +3672,20 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <conditionalFormatting sqref="L4:L8">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"SURPLUS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"DEFISIT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"AMAN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"BELUM"</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 
@@ -3790,7 +3713,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grafik profesional di sebelah kanan dan bawah tabel data</t>
+          <t xml:space="preserve">Grafik profesional di sebelah kanan tabel data</t>
         </is>
       </c>
     </row>
@@ -4878,10 +4801,10 @@
         </is>
       </c>
       <c r="B82" s="3">
-        <f>'Pengeluaran Pangan'!G125</f>
+        <f>SUM('Rekap Harian'!$F$6:$F$36)</f>
       </c>
       <c r="C82" s="6">
-        <f>IF(('Pengeluaran Pangan'!G125+'Pengeluaran Operasional'!G123)=0,0,B82/('Pengeluaran Pangan'!G125+'Pengeluaran Operasional'!G123))</f>
+        <f>IF((SUM('Rekap Harian'!$F$6:$F$36)+SUM('Rekap Harian'!$I$6:$I$36))=0,0,B82/(SUM('Rekap Harian'!$F$6:$F$36)+SUM('Rekap Harian'!$I$6:$I$36)))</f>
       </c>
     </row>
     <row r="83">
@@ -4891,10 +4814,10 @@
         </is>
       </c>
       <c r="B83" s="3">
-        <f>'Pengeluaran Operasional'!G123</f>
+        <f>SUM('Rekap Harian'!$I$6:$I$36)</f>
       </c>
       <c r="C83" s="6">
-        <f>IF(('Pengeluaran Pangan'!G125+'Pengeluaran Operasional'!G123)=0,0,B83/('Pengeluaran Pangan'!G125+'Pengeluaran Operasional'!G123))</f>
+        <f>IF((SUM('Rekap Harian'!$F$6:$F$36)+SUM('Rekap Harian'!$I$6:$I$36))=0,0,B83/(SUM('Rekap Harian'!$F$6:$F$36)+SUM('Rekap Harian'!$I$6:$I$36)))</f>
       </c>
     </row>
     <row r="84">
@@ -4938,7 +4861,7 @@
         <f>Pengaturan!B8</f>
       </c>
       <c r="C87" s="3">
-        <f>'Pengeluaran Pangan'!G125</f>
+        <f>SUM('Rekap Harian'!$F$6:$F$36)</f>
       </c>
       <c r="D87" s="3">
         <f>B87-C87</f>
@@ -4954,7 +4877,7 @@
         <f>Pengaturan!B9</f>
       </c>
       <c r="C88" s="3">
-        <f>'Pengeluaran Operasional'!G123</f>
+        <f>SUM('Rekap Harian'!$I$6:$I$36)</f>
       </c>
       <c r="D88" s="3">
         <f>B88-C88</f>
@@ -5223,14 +5146,14 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Jika Pagu Harian kosong untuk tanggal tertentu, dipakai pagu default</t>
+          <t xml:space="preserve">- Isi aktual pangan &amp; operasional langsung di sheet 'Rekap Harian'</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Dashboard, Rekap Harian, &amp; Grafik update otomatis</t>
+          <t xml:space="preserve">- Dashboard, Rekap Mingguan, &amp; Grafik update otomatis</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5188,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set pagu per tanggal. Biarkan kosong -&gt; pakai pagu default dari sheet Pengaturan</t>
+          <t xml:space="preserve">Set pagu per tanggal. Biarkan default jika pagu hari itu sama dengan Pengaturan</t>
         </is>
       </c>
     </row>
@@ -5756,1177 +5679,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <tabColor rgb="FF548235"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="17"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOG PENGELUARAN BAHAN PANGAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Catat semua transaksi bahan pangan di sini</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tanggal</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Item / Bahan</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kategori</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Qty</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Satuan</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Harga Satuan (Rp)</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jumlah (Rp)</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Keterangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4">
-        <v>46143</v>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Beras premium</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karbohidrat</t>
-        </is>
-      </c>
-      <c r="D4" s="11">
-        <v>50</v>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="F4" s="3">
-        <v>15000</v>
-      </c>
-      <c r="G4" s="9">
-        <f>D4*F4</f>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stok awal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4">
-        <v>46143</v>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ayam potong</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Protein Hewani</t>
-        </is>
-      </c>
-      <c r="D5" s="11">
-        <v>20</v>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="F5" s="3">
-        <v>38000</v>
-      </c>
-      <c r="G5" s="9">
-        <f>D5*F5</f>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Menu hari 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4">
-        <v>46144</v>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sayur bayam</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sayuran</t>
-        </is>
-      </c>
-      <c r="D6" s="11">
-        <v>15</v>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ikat</t>
-        </is>
-      </c>
-      <c r="F6" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G6" s="9">
-        <f>D6*F6</f>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4">
-        <v>46144</v>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telur ayam</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Protein Hewani</t>
-        </is>
-      </c>
-      <c r="D7" s="11">
-        <v>8</v>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="F7" s="3">
-        <v>28000</v>
-      </c>
-      <c r="G7" s="9">
-        <f>D7*F7</f>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4">
-        <v>46145</v>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ikan nila</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Protein Hewani</t>
-        </is>
-      </c>
-      <c r="D8" s="11">
-        <v>18</v>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="F8" s="3">
-        <v>32000</v>
-      </c>
-      <c r="G8" s="9">
-        <f>D8*F8</f>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4">
-        <v>46145</v>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wortel</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sayuran</t>
-        </is>
-      </c>
-      <c r="D9" s="11">
-        <v>10</v>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="F9" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G9" s="9">
-        <f>D9*F9</f>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4">
-        <v>46146</v>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tempe</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Protein Nabati</t>
-        </is>
-      </c>
-      <c r="D10" s="11">
-        <v>12</v>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="F10" s="3">
-        <v>12000</v>
-      </c>
-      <c r="G10" s="9">
-        <f>D10*F10</f>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4">
-        <v>46146</v>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Minyak goreng</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bumbu</t>
-        </is>
-      </c>
-      <c r="D11" s="11">
-        <v>5</v>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">liter</t>
-        </is>
-      </c>
-      <c r="F11" s="3">
-        <v>18000</v>
-      </c>
-      <c r="G11" s="9">
-        <f>D11*F11</f>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4">
-        <v>46147</v>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Buah pisang</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Buah</t>
-        </is>
-      </c>
-      <c r="D12" s="11">
-        <v>20</v>
-      </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sisir</t>
-        </is>
-      </c>
-      <c r="F12" s="3">
-        <v>15000</v>
-      </c>
-      <c r="G12" s="9">
-        <f>D12*F12</f>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4">
-        <v>46147</v>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bumbu dapur</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bumbu</t>
-        </is>
-      </c>
-      <c r="D13" s="11">
-        <v>1</v>
-      </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">paket</t>
-        </is>
-      </c>
-      <c r="F13" s="3">
-        <v>150000</v>
-      </c>
-      <c r="G13" s="9">
-        <f>D13*F13</f>
-      </c>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bawang, cabe</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-</row>
-    <row r="15">
-</row>
-    <row r="16">
-</row>
-    <row r="17">
-</row>
-    <row r="18">
-</row>
-    <row r="19">
-</row>
-    <row r="20">
-</row>
-    <row r="21">
-</row>
-    <row r="22">
-</row>
-    <row r="23">
-</row>
-    <row r="24">
-</row>
-    <row r="25">
-</row>
-    <row r="26">
-</row>
-    <row r="27">
-</row>
-    <row r="28">
-</row>
-    <row r="29">
-</row>
-    <row r="30">
-</row>
-    <row r="31">
-</row>
-    <row r="32">
-</row>
-    <row r="33">
-</row>
-    <row r="34">
-</row>
-    <row r="35">
-</row>
-    <row r="36">
-</row>
-    <row r="37">
-</row>
-    <row r="38">
-</row>
-    <row r="39">
-</row>
-    <row r="40">
-</row>
-    <row r="41">
-</row>
-    <row r="42">
-</row>
-    <row r="43">
-</row>
-    <row r="44">
-</row>
-    <row r="45">
-</row>
-    <row r="46">
-</row>
-    <row r="47">
-</row>
-    <row r="48">
-</row>
-    <row r="49">
-</row>
-    <row r="50">
-</row>
-    <row r="51">
-</row>
-    <row r="52">
-</row>
-    <row r="53">
-</row>
-    <row r="54">
-</row>
-    <row r="55">
-</row>
-    <row r="56">
-</row>
-    <row r="57">
-</row>
-    <row r="58">
-</row>
-    <row r="59">
-</row>
-    <row r="60">
-</row>
-    <row r="61">
-</row>
-    <row r="62">
-</row>
-    <row r="63">
-</row>
-    <row r="64">
-</row>
-    <row r="65">
-</row>
-    <row r="66">
-</row>
-    <row r="67">
-</row>
-    <row r="68">
-</row>
-    <row r="69">
-</row>
-    <row r="70">
-</row>
-    <row r="71">
-</row>
-    <row r="72">
-</row>
-    <row r="73">
-</row>
-    <row r="74">
-</row>
-    <row r="75">
-</row>
-    <row r="76">
-</row>
-    <row r="77">
-</row>
-    <row r="78">
-</row>
-    <row r="79">
-</row>
-    <row r="80">
-</row>
-    <row r="81">
-</row>
-    <row r="82">
-</row>
-    <row r="83">
-</row>
-    <row r="84">
-</row>
-    <row r="85">
-</row>
-    <row r="86">
-</row>
-    <row r="87">
-</row>
-    <row r="88">
-</row>
-    <row r="89">
-</row>
-    <row r="90">
-</row>
-    <row r="91">
-</row>
-    <row r="92">
-</row>
-    <row r="93">
-</row>
-    <row r="94">
-</row>
-    <row r="95">
-</row>
-    <row r="96">
-</row>
-    <row r="97">
-</row>
-    <row r="98">
-</row>
-    <row r="99">
-</row>
-    <row r="100">
-</row>
-    <row r="101">
-</row>
-    <row r="102">
-</row>
-    <row r="103">
-</row>
-    <row r="104">
-</row>
-    <row r="105">
-</row>
-    <row r="106">
-</row>
-    <row r="107">
-</row>
-    <row r="108">
-</row>
-    <row r="109">
-</row>
-    <row r="110">
-</row>
-    <row r="111">
-</row>
-    <row r="112">
-</row>
-    <row r="113">
-</row>
-    <row r="114">
-</row>
-    <row r="115">
-</row>
-    <row r="116">
-</row>
-    <row r="117">
-</row>
-    <row r="118">
-</row>
-    <row r="119">
-</row>
-    <row r="120">
-</row>
-    <row r="121">
-</row>
-    <row r="122">
-</row>
-    <row r="123">
-</row>
-    <row r="124">
-</row>
-    <row r="125">
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTAL PENGELUARAN PANGAN</t>
-        </is>
-      </c>
-      <c r="G125" s="7">
-        <f>SUM(G4:G123)</f>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <tabColor rgb="FFED7D31"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="17"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOG PENGELUARAN OPERASIONAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Catat semua biaya operasional non-bahan pangan di sini</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tanggal</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deskripsi</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kategori</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Qty</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Satuan</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Harga Satuan (Rp)</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jumlah (Rp)</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Keterangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4">
-        <v>46143</v>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gas LPG 12kg</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bahan Bakar</t>
-        </is>
-      </c>
-      <c r="D4" s="11">
-        <v>2</v>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tabung</t>
-        </is>
-      </c>
-      <c r="F4" s="3">
-        <v>185000</v>
-      </c>
-      <c r="G4" s="9">
-        <f>D4*F4</f>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Memasak</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4">
-        <v>46144</v>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gaji juru masak</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tenaga Kerja</t>
-        </is>
-      </c>
-      <c r="D5" s="11">
-        <v>1</v>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">orang</t>
-        </is>
-      </c>
-      <c r="F5" s="3">
-        <v>150000</v>
-      </c>
-      <c r="G5" s="9">
-        <f>D5*F5</f>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Harian</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4">
-        <v>46144</v>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Listrik &amp; air</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Utilitas</t>
-        </is>
-      </c>
-      <c r="D6" s="11">
-        <v>1</v>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bulan</t>
-        </is>
-      </c>
-      <c r="F6" s="3">
-        <v>450000</v>
-      </c>
-      <c r="G6" s="9">
-        <f>D6*F6</f>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4">
-        <v>46145</v>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sabun cuci &amp; pembersih</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sanitasi</t>
-        </is>
-      </c>
-      <c r="D7" s="11">
-        <v>5</v>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pcs</t>
-        </is>
-      </c>
-      <c r="F7" s="3">
-        <v>25000</v>
-      </c>
-      <c r="G7" s="9">
-        <f>D7*F7</f>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4">
-        <v>46146</v>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kemasan makan</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Packaging</t>
-        </is>
-      </c>
-      <c r="D8" s="11">
-        <v>200</v>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pcs</t>
-        </is>
-      </c>
-      <c r="F8" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G8" s="9">
-        <f>D8*F8</f>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4">
-        <v>46147</v>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transportasi distribusi</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transportasi</t>
-        </is>
-      </c>
-      <c r="D9" s="11">
-        <v>1</v>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">trip</t>
-        </is>
-      </c>
-      <c r="F9" s="3">
-        <v>120000</v>
-      </c>
-      <c r="G9" s="9">
-        <f>D9*F9</f>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4">
-        <v>46148</v>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Alat masak (spatula)</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Peralatan</t>
-        </is>
-      </c>
-      <c r="D10" s="11">
-        <v>3</v>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pcs</t>
-        </is>
-      </c>
-      <c r="F10" s="3">
-        <v>35000</v>
-      </c>
-      <c r="G10" s="9">
-        <f>D10*F10</f>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4">
-        <v>46149</v>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Perawatan kompor</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pemeliharaan</t>
-        </is>
-      </c>
-      <c r="D11" s="11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kali</t>
-        </is>
-      </c>
-      <c r="F11" s="3">
-        <v>200000</v>
-      </c>
-      <c r="G11" s="9">
-        <f>D11*F11</f>
-      </c>
-    </row>
-    <row r="12">
-</row>
-    <row r="13">
-</row>
-    <row r="14">
-</row>
-    <row r="15">
-</row>
-    <row r="16">
-</row>
-    <row r="17">
-</row>
-    <row r="18">
-</row>
-    <row r="19">
-</row>
-    <row r="20">
-</row>
-    <row r="21">
-</row>
-    <row r="22">
-</row>
-    <row r="23">
-</row>
-    <row r="24">
-</row>
-    <row r="25">
-</row>
-    <row r="26">
-</row>
-    <row r="27">
-</row>
-    <row r="28">
-</row>
-    <row r="29">
-</row>
-    <row r="30">
-</row>
-    <row r="31">
-</row>
-    <row r="32">
-</row>
-    <row r="33">
-</row>
-    <row r="34">
-</row>
-    <row r="35">
-</row>
-    <row r="36">
-</row>
-    <row r="37">
-</row>
-    <row r="38">
-</row>
-    <row r="39">
-</row>
-    <row r="40">
-</row>
-    <row r="41">
-</row>
-    <row r="42">
-</row>
-    <row r="43">
-</row>
-    <row r="44">
-</row>
-    <row r="45">
-</row>
-    <row r="46">
-</row>
-    <row r="47">
-</row>
-    <row r="48">
-</row>
-    <row r="49">
-</row>
-    <row r="50">
-</row>
-    <row r="51">
-</row>
-    <row r="52">
-</row>
-    <row r="53">
-</row>
-    <row r="54">
-</row>
-    <row r="55">
-</row>
-    <row r="56">
-</row>
-    <row r="57">
-</row>
-    <row r="58">
-</row>
-    <row r="59">
-</row>
-    <row r="60">
-</row>
-    <row r="61">
-</row>
-    <row r="62">
-</row>
-    <row r="63">
-</row>
-    <row r="64">
-</row>
-    <row r="65">
-</row>
-    <row r="66">
-</row>
-    <row r="67">
-</row>
-    <row r="68">
-</row>
-    <row r="69">
-</row>
-    <row r="70">
-</row>
-    <row r="71">
-</row>
-    <row r="72">
-</row>
-    <row r="73">
-</row>
-    <row r="74">
-</row>
-    <row r="75">
-</row>
-    <row r="76">
-</row>
-    <row r="77">
-</row>
-    <row r="78">
-</row>
-    <row r="79">
-</row>
-    <row r="80">
-</row>
-    <row r="81">
-</row>
-    <row r="82">
-</row>
-    <row r="83">
-</row>
-    <row r="84">
-</row>
-    <row r="85">
-</row>
-    <row r="86">
-</row>
-    <row r="87">
-</row>
-    <row r="88">
-</row>
-    <row r="89">
-</row>
-    <row r="90">
-</row>
-    <row r="91">
-</row>
-    <row r="92">
-</row>
-    <row r="93">
-</row>
-    <row r="94">
-</row>
-    <row r="95">
-</row>
-    <row r="96">
-</row>
-    <row r="97">
-</row>
-    <row r="98">
-</row>
-    <row r="99">
-</row>
-    <row r="100">
-</row>
-    <row r="101">
-</row>
-    <row r="102">
-</row>
-    <row r="103">
-</row>
-    <row r="104">
-</row>
-    <row r="105">
-</row>
-    <row r="106">
-</row>
-    <row r="107">
-</row>
-    <row r="108">
-</row>
-    <row r="109">
-</row>
-    <row r="110">
-</row>
-    <row r="111">
-</row>
-    <row r="112">
-</row>
-    <row r="113">
-</row>
-    <row r="114">
-</row>
-    <row r="115">
-</row>
-    <row r="116">
-</row>
-    <row r="117">
-</row>
-    <row r="118">
-</row>
-    <row r="119">
-</row>
-    <row r="120">
-</row>
-    <row r="121">
-</row>
-    <row r="122">
-</row>
-    <row r="123">
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTAL PENGELUARAN OPERASIONAL</t>
-        </is>
-      </c>
-      <c r="G123" s="7">
-        <f>SUM(G4:G121)</f>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF808080"/>
@@ -6947,7 +5699,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gunakan nama kategori yang konsisten agar SUMIF akurat</t>
+          <t xml:space="preserve">Referensi daftar kategori - tidak dipakai di formula, hanya panduan</t>
         </is>
       </c>
     </row>

--- a/Template_Keuangan.xlsx
+++ b/Template_Keuangan.xlsx
@@ -3668,11 +3668,216 @@
         <f>SUM(K4:K8)</f>
       </c>
     </row>
+    <row r="11">
+</row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AKUMULASI PER PERIODE (2-MINGGUAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periode</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rentang Minggu</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pagu Pangan</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aktual Pangan</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selisih Pangan</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pagu Operasional</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aktual Operasional</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selisih Operasional</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total Pagu</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total Aktual</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surplus/Defisit</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status Periode</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periode 1</t>
+        </is>
+      </c>
+      <c r="B14" s="15">
+        <f>"Mg 1 - Mg 2"</f>
+      </c>
+      <c r="C14" s="7">
+        <f>SUM(C4:C5)</f>
+      </c>
+      <c r="D14" s="7">
+        <f>SUM(D4:D5)</f>
+      </c>
+      <c r="E14" s="17">
+        <f>C14-D14</f>
+      </c>
+      <c r="F14" s="7">
+        <f>SUM(F4:F5)</f>
+      </c>
+      <c r="G14" s="7">
+        <f>SUM(G4:G5)</f>
+      </c>
+      <c r="H14" s="17">
+        <f>F14-G14</f>
+      </c>
+      <c r="I14" s="7">
+        <f>C14+F14</f>
+      </c>
+      <c r="J14" s="7">
+        <f>D14+G14</f>
+      </c>
+      <c r="K14" s="17">
+        <f>I14-J14</f>
+      </c>
+      <c r="L14" s="29">
+        <f>IF(J14=0,"",IF(K14&gt;0,"SURPLUS",IF(K14&lt;0,"DEFISIT","AMAN")))</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periode 2</t>
+        </is>
+      </c>
+      <c r="B15" s="15">
+        <f>"Mg 3 - Mg 4"</f>
+      </c>
+      <c r="C15" s="7">
+        <f>SUM(C6:C7)</f>
+      </c>
+      <c r="D15" s="7">
+        <f>SUM(D6:D7)</f>
+      </c>
+      <c r="E15" s="17">
+        <f>C15-D15</f>
+      </c>
+      <c r="F15" s="7">
+        <f>SUM(F6:F7)</f>
+      </c>
+      <c r="G15" s="7">
+        <f>SUM(G6:G7)</f>
+      </c>
+      <c r="H15" s="17">
+        <f>F15-G15</f>
+      </c>
+      <c r="I15" s="7">
+        <f>C15+F15</f>
+      </c>
+      <c r="J15" s="7">
+        <f>D15+G15</f>
+      </c>
+      <c r="K15" s="17">
+        <f>I15-J15</f>
+      </c>
+      <c r="L15" s="29">
+        <f>IF(J15=0,"",IF(K15&gt;0,"SURPLUS",IF(K15&lt;0,"DEFISIT","AMAN")))</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periode 3</t>
+        </is>
+      </c>
+      <c r="B16" s="15">
+        <f>"Mg 5"</f>
+      </c>
+      <c r="C16" s="7">
+        <f>SUM(C8:C8)</f>
+      </c>
+      <c r="D16" s="7">
+        <f>SUM(D8:D8)</f>
+      </c>
+      <c r="E16" s="17">
+        <f>C16-D16</f>
+      </c>
+      <c r="F16" s="7">
+        <f>SUM(F8:F8)</f>
+      </c>
+      <c r="G16" s="7">
+        <f>SUM(G8:G8)</f>
+      </c>
+      <c r="H16" s="17">
+        <f>F16-G16</f>
+      </c>
+      <c r="I16" s="7">
+        <f>C16+F16</f>
+      </c>
+      <c r="J16" s="7">
+        <f>D16+G16</f>
+      </c>
+      <c r="K16" s="17">
+        <f>I16-J16</f>
+      </c>
+      <c r="L16" s="29">
+        <f>IF(J16=0,"",IF(K16&gt;0,"SURPLUS",IF(K16&lt;0,"DEFISIT","AMAN")))</f>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="L4:L8">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"SURPLUS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"DEFISIT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"AMAN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"BELUM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L14:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"SURPLUS"</formula>
     </cfRule>
